--- a/강의예제/8장_실무에서_필요한_데이터_시각화/8장_복습.xlsx
+++ b/강의예제/8장_실무에서_필요한_데이터_시각화/8장_복습.xlsx
@@ -743,7 +743,7 @@
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>① 막대 차트의 세로 축이 600부터 시작한다</t>
+          <t>① 막대 차트의 세로 축이 250부터 시작한다</t>
         </is>
       </c>
       <c r="C5" s="8" t="n"/>
